--- a/data/emploi/emploi.xlsx
+++ b/data/emploi/emploi.xlsx
@@ -10,17 +10,22 @@
     <sheet name="taux_chomage" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="defm_france" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="defm_43" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="flux_france" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="flux_43" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="profil_43" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="caf_rsa" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="caf_rsa_montants_43" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="caf_ppa" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="caf_ppa_age_43" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="caf_aah" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="temps_partiel" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="temps_partiel_raisons" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="emplois_vacants" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="defm_departements" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="departements_noms" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="defm_france_janvier" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="flux_france" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="flux_43" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="profil_43" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="caf_rsa" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="caf_rsa_montants_43" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="caf_ppa" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="caf_ppa_age_43" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="caf_aah" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="temps_partiel" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="temps_partiel_raisons" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="temps_partiel_quotite" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="emplois_vacants" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="constantes" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,8 +435,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1067,155 +1072,320 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>geo</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>anciennete</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>foyers</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>personnes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Entre 40 et 44 ans</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1472</v>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Entre 2012 et 2013</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Entre 60 et 64 ans</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>482</v>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Entre 2014 et 2015</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Moins de 20 ans</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Entre 2020 et 2021</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>344</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Entre 50 et 54 ans</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>31</v>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Entre 2018 et 2019</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>309</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>65 ans ou plus</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>44</v>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Entre 2024 et 2025</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>988</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Entre 25 et 29 ans</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1855</v>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Avant 2010</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>204</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Entre 45 et 49 ans</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1327</v>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Entre 2016 et 2017</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Entre 30 et 34 ans</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>135</v>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Entre 2022 et 2023</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>402</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Entre 35 et 39 ans</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1501</v>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Entre 20 et 24 ans</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2101</v>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Avant 2010</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>192483</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Entre 55 et 59 ans</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>950</v>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Entre 2010 et 2011</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>67976</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Age indÃÂ©terminÃÂ©</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Entre 2012 et 2013</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>86288</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Entre 2014 et 2015</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>103518</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t># Feuille : caf_ppa_age_43</t>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Entre 2016 et 2017</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>146377</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Entre 2018 et 2019</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>206449</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Entre 2020 et 2021</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>211921</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Entre 2022 et 2023</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>276296</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Entre 2024 et 2025</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>535015</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Inconnu</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t># Feuille : caf_rsa</t>
         </is>
       </c>
     </row>
@@ -1230,501 +1400,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>sexe</t>
+          <t>montant</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>nombre</t>
+          <t>foyers</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>RSA majorÃÂ©</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Entre 45 et 49 ans</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>344</v>
+          <t>Entre 400 et 599 Ã¢ÂÂ¬</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>RSA non majorÃÂ©</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Entre 20 et 24 ans</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>126</v>
+          <t>Entre 200 et 399 Ã¢ÂÂ¬</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>RSA non majorÃÂ©</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Entre 30 et 34 ans</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>185</v>
+          <t>800 Ã¢ÂÂ¬ ou plus</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>RSA majorÃÂ©</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Entre 45 et 49 ans</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>360</v>
+          <t>Entre 600 et 799 Ã¢ÂÂ¬</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>RSA majorÃÂ©</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Entre 50 et 54 ans</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>501</v>
+          <t>Entre 200 et 399 Ã¢ÂÂ¬</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>RSA majorÃÂ©</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Entre 55 et 59 ans</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>626</v>
+          <t>800 Ã¢ÂÂ¬ ou plus</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>101</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>RSA non majorÃÂ©</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>65 ans ou plus</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>351</v>
+          <t>Moins de 200 Ã¢ÂÂ¬</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>259</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>RSA non majorÃÂ©</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Entre 35 et 39 ans</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>261</v>
+          <t>Entre 600 et 799 Ã¢ÂÂ¬</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>463</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>RSA non majorÃÂ©</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Entre 60 et 64 ans</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Entre 60 et 64 ans</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>418</v>
+          <t>Entre 400 et 599 Ã¢ÂÂ¬</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1294</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Entre 30 et 34 ans</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>65 ans ou plus</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Entre 35 et 39 ans</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Moins de 20 ans</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Entre 20 et 24 ans</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Entre 40 et 44 ans</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Entre 50 et 54 ans</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Entre 55 et 59 ans</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Moins de 20 ans</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Entre 25 et 29 ans</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Entre 40 et 44 ans</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>689655</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Femme</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>688455</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t># Feuille : caf_aah</t>
+          <t># Feuille : caf_rsa_montants_43</t>
         </is>
       </c>
     </row>
@@ -1739,178 +1578,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>annee</t>
+          <t>geo</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>nombreMilliers</t>
+          <t>groupe</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>partPourcent</t>
+          <t>foyers</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>personnes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>montantTotal</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>4654</v>
-      </c>
-      <c r="C2" t="n">
-        <v>20.1</v>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Seul avec enfants</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>4525</v>
-      </c>
-      <c r="C3" t="n">
-        <v>19.9</v>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Couple avec enfants</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>4589</v>
-      </c>
-      <c r="C4" t="n">
-        <v>20</v>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Seul sans enfant</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4534</v>
-      </c>
-      <c r="C5" t="n">
-        <v>19.6</v>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Couple sans enfant</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4415</v>
-      </c>
-      <c r="C6" t="n">
-        <v>19.1</v>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Seul avec enfants</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>4190</v>
-      </c>
-      <c r="C7" t="n">
-        <v>18.2</v>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Couple avec enfants</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>4214</v>
-      </c>
-      <c r="C8" t="n">
-        <v>18.1</v>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Seul sans enfant</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4143</v>
-      </c>
-      <c r="C9" t="n">
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>4193</v>
-      </c>
-      <c r="C10" t="n">
-        <v>17.3</v>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Couple sans enfant</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>4152</v>
-      </c>
-      <c r="C11" t="n">
-        <v>17.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4229</v>
-      </c>
-      <c r="C12" t="n">
-        <v>17.6</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t># Feuille : temps_partiel</t>
+          <t># Feuille : caf_ppa</t>
         </is>
       </c>
     </row>
@@ -1925,140 +1729,155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>annee</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>raison</t>
+          <t>foyers</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>personnes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Pour d'autres raisons - Exerce une autre activitÃÂ© professionnelle</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>6.6</v>
+          <t>Entre 40 et 44 ans</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1472</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pour d'autres raisons - Pour raison de santÃÂ© ou de handicap</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>13</v>
+          <t>Entre 60 et 64 ans</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>482</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Pour d'autres raisons - Pour disposer dÃ¢ÂÂun revenu dÃ¢ÂÂappoint (en plus des ÃÂ©tudes, retraite, etc.)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>5.3</v>
+          <t>Moins de 20 ans</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NÃ¢ÂÂa pas trouvÃÂ© dÃ¢ÂÂemploi ÃÂ  temps complet</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>21.3</v>
+          <t>Entre 50 et 54 ans</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Pour d'autres raisons - Pour sÃ¢ÂÂoccuper de ses enfants ou dÃ¢ÂÂun proche</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>25.4</v>
+          <t>65 ans ou plus</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Pour d'autres raisons - Pour suivre des ÃÂ©tudes ou une formation</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>7.1</v>
+          <t>Entre 25 et 29 ans</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1855</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Pour d'autres raisons - Pour avoir du temps libre</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>16</v>
+          <t>Entre 45 et 49 ans</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Entre 30 et 34 ans</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>135</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t># Feuille : temps_partiel_raisons</t>
+          <t>Entre 35 et 39 ans</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Entre 20 et 24 ans</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Entre 55 et 59 ans</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Age indÃÂ©terminÃÂ©</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t># Feuille : caf_ppa_age_43</t>
         </is>
       </c>
     </row>
@@ -2073,12 +1892,898 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>geo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sexe</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>nombre</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Entre 45 et 49 ans</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Entre 20 et 24 ans</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Entre 30 et 34 ans</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Entre 45 et 49 ans</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Entre 50 et 54 ans</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Entre 55 et 59 ans</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>65 ans ou plus</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Entre 35 et 39 ans</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Entre 60 et 64 ans</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Entre 60 et 64 ans</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Entre 30 et 34 ans</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>65 ans ou plus</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Entre 35 et 39 ans</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Moins de 20 ans</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Entre 20 et 24 ans</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Entre 40 et 44 ans</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Entre 50 et 54 ans</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Entre 55 et 59 ans</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Moins de 20 ans</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Entre 25 et 29 ans</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Entre 40 et 44 ans</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>689655</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>688455</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t># Feuille : caf_aah</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>annee</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nombreMilliers</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>partPourcent</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4654</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4525</v>
+      </c>
+      <c r="C3" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4589</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4534</v>
+      </c>
+      <c r="C5" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4415</v>
+      </c>
+      <c r="C6" t="n">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4190</v>
+      </c>
+      <c r="C7" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4214</v>
+      </c>
+      <c r="C8" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4143</v>
+      </c>
+      <c r="C9" t="n">
+        <v>17.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4193</v>
+      </c>
+      <c r="C10" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4152</v>
+      </c>
+      <c r="C11" t="n">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4229</v>
+      </c>
+      <c r="C12" t="n">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t># Feuille : temps_partiel</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>annee</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>raison</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>part</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pour d'autres raisons - Exerce une autre activitÃÂ© professionnelle</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pour d'autres raisons - Pour raison de santÃÂ© ou de handicap</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Pour d'autres raisons - Pour disposer dÃ¢ÂÂun revenu dÃ¢ÂÂappoint (en plus des ÃÂ©tudes, retraite, etc.)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NÃ¢ÂÂa pas trouvÃÂ© dÃ¢ÂÂemploi ÃÂ  temps complet</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pour d'autres raisons - Pour sÃ¢ÂÂoccuper de ses enfants ou dÃ¢ÂÂun proche</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Pour d'autres raisons - Pour suivre des ÃÂ©tudes ou une formation</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pour d'autres raisons - Pour avoir du temps libre</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t># Feuille : temps_partiel_raisons</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>annee</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>quotite</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>part</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t># Feuille : temps_partiel_quotite</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2882,6 +3587,275 @@
       <c r="A63" t="inlineStr">
         <is>
           <t># Feuille : emplois_vacants</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cle</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>valeur</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>unite</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>are_coef_partie_variable</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>taux</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ARE : part du SJR (40,4 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>are_partie_fixe</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>euros/jour</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ARE : partie fixe par jour (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>are_coef_min</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>taux</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ARE : 57 % du SJR (minimum garanti)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>are_plancher_jour</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>euros/jour</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ARE : allocation journalière minimale (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>are_plafond_coef</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>taux</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ARE : allocation &lt;= 75 % du salaire journalier de référence</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>are_jours_min</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>130</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>jours</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ARE : jours travaillés exigés sur les 24 derniers mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cotis_chomage_salarie_pct</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Cotisation chômage des salariés : 0 % depuis 2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cotis_chomage_employeur_pct</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Cotisation chômage payée uniquement par l'employeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rsa_socle</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>651.6900000000001</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>euros/mois</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RSA socle pour une personne seule (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>smic_horaire_brut</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>euros/h</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SMIC horaire brut (2026) — à ajuster chaque année</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ppa_exonerations_patronales_md</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>80</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Md€/an</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Exonérations de cotisations patronales (voir page économie)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t># Feuille : constantes</t>
         </is>
       </c>
     </row>
@@ -2900,15 +3874,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7730,15 +8704,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11848,15 +12822,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11867,276 +12843,44 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>entrees</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>sorties</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>radiations</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>reprisesEmploi</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>cessationsDefautActualisation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>6278700</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5977200</v>
-      </c>
-      <c r="D2" t="n">
-        <v>526400</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1167300</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2620600</v>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>6805200</v>
-      </c>
-      <c r="C3" t="n">
-        <v>6777900</v>
-      </c>
-      <c r="D3" t="n">
-        <v>621100</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1270800</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2838200</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>6738300</v>
-      </c>
-      <c r="C4" t="n">
-        <v>6557800</v>
-      </c>
-      <c r="D4" t="n">
-        <v>607600</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1310800</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2733000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>6488900</v>
-      </c>
-      <c r="C5" t="n">
-        <v>6476600</v>
-      </c>
-      <c r="D5" t="n">
-        <v>545400</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1306500</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2875400</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>6537000</v>
-      </c>
-      <c r="C6" t="n">
-        <v>6084600</v>
-      </c>
-      <c r="D6" t="n">
-        <v>547900</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1387800</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2930500</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6204800</v>
-      </c>
-      <c r="C7" t="n">
-        <v>5892600</v>
-      </c>
-      <c r="D7" t="n">
-        <v>326700</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1241800</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2650100</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>6271300</v>
-      </c>
-      <c r="C8" t="n">
-        <v>6654500</v>
-      </c>
-      <c r="D8" t="n">
-        <v>525200</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1493800</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2678700</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>6530600</v>
-      </c>
-      <c r="C9" t="n">
-        <v>6774500</v>
-      </c>
-      <c r="D9" t="n">
-        <v>634200</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1184800</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3053900</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>6674200</v>
-      </c>
-      <c r="C10" t="n">
-        <v>6613100</v>
-      </c>
-      <c r="D10" t="n">
-        <v>681200</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1046000</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3005400</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>6662700</v>
-      </c>
-      <c r="C11" t="n">
-        <v>6521000</v>
-      </c>
-      <c r="D11" t="n">
-        <v>661000</v>
-      </c>
-      <c r="E11" t="n">
-        <v>984900</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3047900</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>8733400</v>
-      </c>
-      <c r="C12" t="n">
-        <v>8532700</v>
-      </c>
-      <c r="D12" t="n">
-        <v>248900</v>
-      </c>
-      <c r="E12" t="n">
-        <v>886500</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2756500</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t># Feuille : flux_france</t>
+          <t># Feuille : defm_departements</t>
         </is>
       </c>
     </row>
@@ -12151,1855 +12895,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C143"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>entrees</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sorties</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1490</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1330</v>
+          <t>nom</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2015-02</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1210</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2015-03</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1320</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2015-04</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1250</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2015-05</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2015-06</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1390</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1390</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2015-07</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1810</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2015-08</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2015-09</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2140</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1940</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2015-10</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1690</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2015-11</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1490</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1630</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2015-12</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1570</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2016-01</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1470</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1480</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2016-02</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1260</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1390</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2016-03</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1410</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1660</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2016-04</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1350</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1740</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2016-05</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2016-06</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1540</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2016-07</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>2030</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2016-08</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1680</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2016-09</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2160</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2016-10</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1700</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1940</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2016-11</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1520</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2016-12</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1620</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1570</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2017-01</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1690</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1570</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2017-02</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1310</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2017-03</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1430</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2017-04</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1320</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2017-05</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1350</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2017-06</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1400</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2017-07</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2060</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2017-08</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1580</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2017-09</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1980</v>
-      </c>
-      <c r="C34" t="n">
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2017-10</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1700</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1790</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2017-11</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1560</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2017-12</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1400</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2018-01</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1540</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2018-02</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1230</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2018-03</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1260</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2018-04</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1350</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2018-05</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1340</v>
-      </c>
-      <c r="C42" t="n">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2018-06</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1350</v>
-      </c>
-      <c r="C43" t="n">
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2018-07</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C44" t="n">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2018-08</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>1620</v>
-      </c>
-      <c r="C45" t="n">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2018-09</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>1960</v>
-      </c>
-      <c r="C46" t="n">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2018-10</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>1710</v>
-      </c>
-      <c r="C47" t="n">
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2018-11</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1520</v>
-      </c>
-      <c r="C48" t="n">
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2018-12</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1320</v>
-      </c>
-      <c r="C49" t="n">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2019-01</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1720</v>
-      </c>
-      <c r="C50" t="n">
-        <v>1510</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2019-02</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1150</v>
-      </c>
-      <c r="C51" t="n">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2019-03</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1350</v>
-      </c>
-      <c r="C52" t="n">
-        <v>1610</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2019-04</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1370</v>
-      </c>
-      <c r="C53" t="n">
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2019-05</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1400</v>
-      </c>
-      <c r="C54" t="n">
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2019-06</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1480</v>
-      </c>
-      <c r="C55" t="n">
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2019-07</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>2060</v>
-      </c>
-      <c r="C56" t="n">
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2019-08</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1490</v>
-      </c>
-      <c r="C57" t="n">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2019-09</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2060</v>
-      </c>
-      <c r="C58" t="n">
-        <v>2230</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2019-10</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1660</v>
-      </c>
-      <c r="C59" t="n">
-        <v>1780</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2019-11</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1370</v>
-      </c>
-      <c r="C60" t="n">
-        <v>1640</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2019-12</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>1440</v>
-      </c>
-      <c r="C61" t="n">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2020-01</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>1560</v>
-      </c>
-      <c r="C62" t="n">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2020-02</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>1250</v>
-      </c>
-      <c r="C63" t="n">
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2020-03</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>1400</v>
-      </c>
-      <c r="C64" t="n">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2020-04</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>1130</v>
-      </c>
-      <c r="C65" t="n">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2020-05</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>950</v>
-      </c>
-      <c r="C66" t="n">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2020-06</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>1420</v>
-      </c>
-      <c r="C67" t="n">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2020-07</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>1700</v>
-      </c>
-      <c r="C68" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2020-08</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>1460</v>
-      </c>
-      <c r="C69" t="n">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2020-09</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C70" t="n">
-        <v>1940</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2020-10</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>1450</v>
-      </c>
-      <c r="C71" t="n">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2020-11</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>1420</v>
-      </c>
-      <c r="C72" t="n">
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2020-12</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>1340</v>
-      </c>
-      <c r="C73" t="n">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2021-01</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>1430</v>
-      </c>
-      <c r="C74" t="n">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2021-02</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>1210</v>
-      </c>
-      <c r="C75" t="n">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2021-03</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>1260</v>
-      </c>
-      <c r="C76" t="n">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2021-04</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C77" t="n">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2021-05</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>1170</v>
-      </c>
-      <c r="C78" t="n">
-        <v>1390</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2021-06</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>1400</v>
-      </c>
-      <c r="C79" t="n">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2021-07</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>1760</v>
-      </c>
-      <c r="C80" t="n">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2021-08</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>1570</v>
-      </c>
-      <c r="C81" t="n">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2021-09</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>1870</v>
-      </c>
-      <c r="C82" t="n">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2021-10</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>1490</v>
-      </c>
-      <c r="C83" t="n">
-        <v>1860</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2021-11</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>1350</v>
-      </c>
-      <c r="C84" t="n">
-        <v>1540</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2021-12</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1360</v>
-      </c>
-      <c r="C85" t="n">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2022-01</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>1560</v>
-      </c>
-      <c r="C86" t="n">
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2022-02</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>1140</v>
-      </c>
-      <c r="C87" t="n">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2022-03</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C88" t="n">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2022-04</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>1170</v>
-      </c>
-      <c r="C89" t="n">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2022-05</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>1280</v>
-      </c>
-      <c r="C90" t="n">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2022-06</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>1380</v>
-      </c>
-      <c r="C91" t="n">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2022-07</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>1670</v>
-      </c>
-      <c r="C92" t="n">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2022-08</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>1580</v>
-      </c>
-      <c r="C93" t="n">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2022-09</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>1860</v>
-      </c>
-      <c r="C94" t="n">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2022-10</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>1590</v>
-      </c>
-      <c r="C95" t="n">
-        <v>1720</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2022-11</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>1520</v>
-      </c>
-      <c r="C96" t="n">
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2022-12</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>1400</v>
-      </c>
-      <c r="C97" t="n">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2023-01</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>1700</v>
-      </c>
-      <c r="C98" t="n">
-        <v>1540</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2023-02</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>1240</v>
-      </c>
-      <c r="C99" t="n">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2023-03</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>1310</v>
-      </c>
-      <c r="C100" t="n">
-        <v>1480</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2023-04</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>1290</v>
-      </c>
-      <c r="C101" t="n">
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2023-05</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>1290</v>
-      </c>
-      <c r="C102" t="n">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2023-06</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>1350</v>
-      </c>
-      <c r="C103" t="n">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2023-07</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>1900</v>
-      </c>
-      <c r="C104" t="n">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2023-08</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>1540</v>
-      </c>
-      <c r="C105" t="n">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2023-09</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>1830</v>
-      </c>
-      <c r="C106" t="n">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2023-10</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>1600</v>
-      </c>
-      <c r="C107" t="n">
-        <v>1760</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2023-11</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>1530</v>
-      </c>
-      <c r="C108" t="n">
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2023-12</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>1340</v>
-      </c>
-      <c r="C109" t="n">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>1580</v>
-      </c>
-      <c r="C110" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>2024-02</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>1210</v>
-      </c>
-      <c r="C111" t="n">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>1370</v>
-      </c>
-      <c r="C112" t="n">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>1280</v>
-      </c>
-      <c r="C113" t="n">
-        <v>1460</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2024-05</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>1320</v>
-      </c>
-      <c r="C114" t="n">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>1350</v>
-      </c>
-      <c r="C115" t="n">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2024-07</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>1750</v>
-      </c>
-      <c r="C116" t="n">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2024-08</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>1390</v>
-      </c>
-      <c r="C117" t="n">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2024-09</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>1940</v>
-      </c>
-      <c r="C118" t="n">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2024-10</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>1570</v>
-      </c>
-      <c r="C119" t="n">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2024-11</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>1320</v>
-      </c>
-      <c r="C120" t="n">
-        <v>1420</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>1290</v>
-      </c>
-      <c r="C121" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>1830</v>
-      </c>
-      <c r="C122" t="n">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>1100</v>
-      </c>
-      <c r="C123" t="n">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>1360</v>
-      </c>
-      <c r="C124" t="n">
-        <v>1570</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>1540</v>
-      </c>
-      <c r="C125" t="n">
-        <v>1740</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C126" t="n">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>1750</v>
-      </c>
-      <c r="C127" t="n">
-        <v>1720</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>2220</v>
-      </c>
-      <c r="C128" t="n">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>1920</v>
-      </c>
-      <c r="C129" t="n">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>2460</v>
-      </c>
-      <c r="C130" t="n">
-        <v>2230</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>2100</v>
-      </c>
-      <c r="C131" t="n">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C132" t="n">
-        <v>2150</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>1940</v>
-      </c>
-      <c r="C133" t="n">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>2220</v>
-      </c>
-      <c r="C134" t="n">
-        <v>2430</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>1950</v>
-      </c>
-      <c r="C135" t="n">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>2070</v>
-      </c>
-      <c r="C136" t="n">
-        <v>2230</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>2010</v>
-      </c>
-      <c r="C137" t="n">
-        <v>2180</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C138" t="n">
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>2190</v>
-      </c>
-      <c r="C139" t="n">
-        <v>2170</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>2490</v>
-      </c>
-      <c r="C140" t="n">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>2390</v>
-      </c>
-      <c r="C141" t="n">
-        <v>2170</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t># Feuille : flux_43</t>
+          <t># Feuille : departements_noms</t>
         </is>
       </c>
     </row>
@@ -14014,297 +12932,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>annee</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>categorie</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>sexe</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>tranche</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>nombre</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Moins de 25 ans</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1450</v>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Moins de 25 ans</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2570</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>25 ÃÂ  49 ans</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>8810</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>50 ans et plus</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2240</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>50 ans et plus</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4620</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>25 ÃÂ  49 ans</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>3990</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Femmes</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>8540</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Hommes</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>3930</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Femmes</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>3750</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Hommes</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>7460</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t># Feuille : profil_43</t>
+          <t># Feuille : defm_france_janvier</t>
         </is>
       </c>
     </row>
@@ -14319,320 +12999,295 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>annee</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>anciennete</t>
+          <t>entrees</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>foyers</t>
+          <t>sorties</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>radiations</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>reprisesEmploi</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cessationsDefautActualisation</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Entre 2012 et 2013</t>
-        </is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>6278700</v>
       </c>
       <c r="C2" t="n">
-        <v>128</v>
+        <v>5977200</v>
+      </c>
+      <c r="D2" t="n">
+        <v>526400</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1167300</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2620600</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Entre 2014 et 2015</t>
-        </is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6805200</v>
       </c>
       <c r="C3" t="n">
-        <v>160</v>
+        <v>6777900</v>
+      </c>
+      <c r="D3" t="n">
+        <v>621100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1270800</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2838200</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Entre 2020 et 2021</t>
-        </is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>6738300</v>
       </c>
       <c r="C4" t="n">
-        <v>344</v>
+        <v>6557800</v>
+      </c>
+      <c r="D4" t="n">
+        <v>607600</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1310800</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2733000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Entre 2018 et 2019</t>
-        </is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>6488900</v>
       </c>
       <c r="C5" t="n">
-        <v>309</v>
+        <v>6476600</v>
+      </c>
+      <c r="D5" t="n">
+        <v>545400</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1306500</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2875400</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Entre 2024 et 2025</t>
-        </is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6537000</v>
       </c>
       <c r="C6" t="n">
-        <v>988</v>
+        <v>6084600</v>
+      </c>
+      <c r="D6" t="n">
+        <v>547900</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1387800</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2930500</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Avant 2010</t>
-        </is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6204800</v>
       </c>
       <c r="C7" t="n">
-        <v>204</v>
+        <v>5892600</v>
+      </c>
+      <c r="D7" t="n">
+        <v>326700</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1241800</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2650100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Entre 2016 et 2017</t>
-        </is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>6271300</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>6654500</v>
+      </c>
+      <c r="D8" t="n">
+        <v>525200</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1493800</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2678700</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Entre 2022 et 2023</t>
-        </is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6530600</v>
       </c>
       <c r="C9" t="n">
-        <v>402</v>
+        <v>6774500</v>
+      </c>
+      <c r="D9" t="n">
+        <v>634200</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1184800</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3053900</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6674200</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>6613100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>681200</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1046000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3005400</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Avant 2010</t>
-        </is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>6662700</v>
       </c>
       <c r="C11" t="n">
-        <v>192483</v>
+        <v>6521000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>661000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>984900</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3047900</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Entre 2010 et 2011</t>
-        </is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>8733400</v>
       </c>
       <c r="C12" t="n">
-        <v>67976</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Entre 2012 et 2013</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>86288</v>
+        <v>8532700</v>
+      </c>
+      <c r="D12" t="n">
+        <v>248900</v>
+      </c>
+      <c r="E12" t="n">
+        <v>886500</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2756500</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Entre 2014 et 2015</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>103518</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Entre 2016 et 2017</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>146377</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Entre 2018 et 2019</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>206449</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Entre 2020 et 2021</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>211921</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Entre 2022 et 2023</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>276296</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Entre 2024 et 2025</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>535015</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t># Feuille : caf_rsa</t>
+          <t># Feuille : flux_france</t>
         </is>
       </c>
     </row>
@@ -14647,170 +13302,1855 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>montant</t>
+          <t>entrees</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>foyers</t>
+          <t>sorties</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RSA majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Entre 400 et 599 Ã¢ÂÂ¬</t>
-        </is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1490</v>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RSA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Entre 200 et 399 Ã¢ÂÂ¬</t>
-        </is>
+          <t>2015-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1210</v>
       </c>
       <c r="C3" t="n">
-        <v>294</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RSA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>800 Ã¢ÂÂ¬ ou plus</t>
-        </is>
+          <t>2015-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1320</v>
       </c>
       <c r="C4" t="n">
-        <v>218</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RSA majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Entre 600 et 799 Ã¢ÂÂ¬</t>
-        </is>
+          <t>2015-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1250</v>
       </c>
       <c r="C5" t="n">
-        <v>120</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RSA majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Entre 200 et 399 Ã¢ÂÂ¬</t>
-        </is>
+          <t>2015-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1100</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RSA majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>800 Ã¢ÂÂ¬ ou plus</t>
-        </is>
+          <t>2015-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1390</v>
       </c>
       <c r="C7" t="n">
-        <v>101</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RSA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Moins de 200 Ã¢ÂÂ¬</t>
-        </is>
+          <t>2015-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1810</v>
       </c>
       <c r="C8" t="n">
-        <v>259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RSA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Entre 600 et 799 Ã¢ÂÂ¬</t>
-        </is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1500</v>
       </c>
       <c r="C9" t="n">
-        <v>463</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RSA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Entre 400 et 599 Ã¢ÂÂ¬</t>
-        </is>
+          <t>2015-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2140</v>
       </c>
       <c r="C10" t="n">
-        <v>1294</v>
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2015-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1690</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1750</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t># Feuille : caf_rsa_montants_43</t>
+          <t>2015-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1490</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2015-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1570</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2016-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1470</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2016-02</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2016-03</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1410</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2016-04</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2016-05</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2016-06</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1540</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2016-07</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2016-08</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2016-09</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2160</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2016-10</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1700</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2016-11</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1520</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2016-12</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1620</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1690</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2017-02</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1310</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2017-03</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2017-04</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1320</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2017-05</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2017-06</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2017-07</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2060</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2017-08</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2017-09</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2017-10</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1700</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2017-11</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1560</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2017-12</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2018-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1540</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1230</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1340</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1620</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1960</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1710</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1520</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1320</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1720</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2019-02</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1150</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2019-03</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2019-04</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2019-05</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1480</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2019-07</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2060</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1490</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2060</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1660</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1440</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1560</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1130</v>
+      </c>
+      <c r="C65" t="n">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>950</v>
+      </c>
+      <c r="C66" t="n">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1420</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1700</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1460</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1450</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1420</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1340</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1210</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1170</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1760</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1570</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1870</v>
+      </c>
+      <c r="C82" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1490</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1360</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1560</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1140</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1170</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1280</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1380</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1670</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1860</v>
+      </c>
+      <c r="C94" t="n">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1590</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1520</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1400</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1700</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1240</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1310</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1290</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1290</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1900</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1540</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1830</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1530</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1340</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1210</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1280</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1320</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1390</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1570</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1320</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1290</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1830</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1360</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1540</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>2220</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>2460</v>
+      </c>
+      <c r="C130" t="n">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C131" t="n">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C132" t="n">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2220</v>
+      </c>
+      <c r="C134" t="n">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1950</v>
+      </c>
+      <c r="C135" t="n">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>2070</v>
+      </c>
+      <c r="C136" t="n">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C137" t="n">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C138" t="n">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>2190</v>
+      </c>
+      <c r="C139" t="n">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>2490</v>
+      </c>
+      <c r="C140" t="n">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>2390</v>
+      </c>
+      <c r="C141" t="n">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t># Feuille : flux_43</t>
         </is>
       </c>
     </row>
@@ -14825,657 +15165,297 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>geo</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>categorie</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>situation</t>
+          <t>sexe</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>foyers</t>
+          <t>tranche</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>personnes</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>montantTotal</t>
+          <t>nombre</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PA majorÃÂ©</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Seul avec 2 enfants ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>240</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Moins de 25 ans</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1450</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PA non majorÃÂ©</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Couple avec 1 enfant ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>695</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Moins de 25 ans</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2570</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PA non majorÃÂ©</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Couple avec 3 enfants ou plus ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>420</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>25 ÃÂ  49 ans</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>8810</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PA non majorÃÂ©</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>46</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>50 ans et plus</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2240</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PA majorÃÂ©</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seul avec 1 enfant ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>281</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>50 ans et plus</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4620</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PA non majorÃÂ©</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seul sans enfant ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>7810</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>25 ÃÂ  49 ans</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3990</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PA non majorÃÂ©</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seul avec 1 enfant ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1216</v>
+          <t>Femmes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>8540</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PA non majorÃÂ©</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Couple sans enfant ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>648</v>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3930</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PA non majorÃÂ©</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Couple avec 2 enfants ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>899</v>
+          <t>Femmes</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3750</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PA majorÃÂ©</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seul avec 3 enfants ou plus ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Seul avec 2 enfants ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>763</v>
+          <t>Hommes</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>7460</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Seul avec 3 enfants ou plus ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PA majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>24</v>
-      </c>
-      <c r="E14" t="n">
-        <v>62</v>
-      </c>
-      <c r="F14" t="n">
-        <v>8950</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PA majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Seul avec 1 enfant ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>92688</v>
-      </c>
-      <c r="E15" t="n">
-        <v>188294</v>
-      </c>
-      <c r="F15" t="n">
-        <v>27565798</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PA majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Seul avec 2 enfants ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>69026</v>
-      </c>
-      <c r="E16" t="n">
-        <v>207223</v>
-      </c>
-      <c r="F16" t="n">
-        <v>23805522</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PA majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Seul avec 3 enfants ou plus ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>37942</v>
-      </c>
-      <c r="E17" t="n">
-        <v>170602</v>
-      </c>
-      <c r="F17" t="n">
-        <v>11012243</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PA majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Seul sans enfant ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>19193</v>
-      </c>
-      <c r="E18" t="n">
-        <v>28737</v>
-      </c>
-      <c r="F18" t="n">
-        <v>4733428</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>PA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Couple avec 1 enfant ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>251104</v>
-      </c>
-      <c r="E19" t="n">
-        <v>748876</v>
-      </c>
-      <c r="F19" t="n">
-        <v>57042476</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>PA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Couple avec 2 enfants ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>280201</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1108019</v>
-      </c>
-      <c r="F20" t="n">
-        <v>68596861</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Couple avec 3 enfants ou plus ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>233786</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1279905</v>
-      </c>
-      <c r="F21" t="n">
-        <v>58926210</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>PA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Couple sans enfant ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>247367</v>
-      </c>
-      <c r="E22" t="n">
-        <v>494142</v>
-      </c>
-      <c r="F22" t="n">
-        <v>46671247</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>PA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>5015</v>
-      </c>
-      <c r="E23" t="n">
-        <v>9233</v>
-      </c>
-      <c r="F23" t="n">
-        <v>928791</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>PA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Seul avec 1 enfant ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>460195</v>
-      </c>
-      <c r="E24" t="n">
-        <v>892869</v>
-      </c>
-      <c r="F24" t="n">
-        <v>109032190</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>PA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Seul avec 2 enfants ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>245747</v>
-      </c>
-      <c r="E25" t="n">
-        <v>717235</v>
-      </c>
-      <c r="F25" t="n">
-        <v>55030977</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>PA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Seul avec 3 enfants ou plus ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>69774</v>
-      </c>
-      <c r="E26" t="n">
-        <v>293987</v>
-      </c>
-      <c r="F26" t="n">
-        <v>13135037</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>PA non majorÃÂ©</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Seul sans enfant ÃÂ  charge</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>2572092</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2598013</v>
-      </c>
-      <c r="F27" t="n">
-        <v>351352427</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t># Feuille : caf_ppa</t>
+          <t># Feuille : profil_43</t>
         </is>
       </c>
     </row>

--- a/data/emploi/emploi.xlsx
+++ b/data/emploi/emploi.xlsx
@@ -25,7 +25,8 @@
     <sheet name="temps_partiel_raisons" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="temps_partiel_quotite" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="emplois_vacants" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="constantes" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="creations_entreprises" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="constantes" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1428,12 +1429,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RSA majorÃ©</t>
+          <t>RSA majorÃÂÃÂ©</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Entre 400 et 599 â¬</t>
+          <t>Entre 400 et 599 ÃÂ¢ÃÂÃÂ¬</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1443,12 +1444,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RSA non majorÃ©</t>
+          <t>RSA non majorÃÂÃÂ©</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Entre 200 et 399 â¬</t>
+          <t>Entre 200 et 399 ÃÂ¢ÃÂÃÂ¬</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1458,12 +1459,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RSA non majorÃ©</t>
+          <t>RSA non majorÃÂÃÂ©</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>800 â¬ ou plus</t>
+          <t>800 ÃÂ¢ÃÂÃÂ¬ ou plus</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1473,12 +1474,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RSA majorÃ©</t>
+          <t>RSA majorÃÂÃÂ©</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Entre 600 et 799 â¬</t>
+          <t>Entre 600 et 799 ÃÂ¢ÃÂÃÂ¬</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1488,12 +1489,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RSA majorÃ©</t>
+          <t>RSA majorÃÂÃÂ©</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Entre 200 et 399 â¬</t>
+          <t>Entre 200 et 399 ÃÂ¢ÃÂÃÂ¬</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1503,12 +1504,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RSA majorÃ©</t>
+          <t>RSA majorÃÂÃÂ©</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>800 â¬ ou plus</t>
+          <t>800 ÃÂ¢ÃÂÃÂ¬ ou plus</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1518,12 +1519,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RSA non majorÃ©</t>
+          <t>RSA non majorÃÂÃÂ©</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Moins de 200 â¬</t>
+          <t>Moins de 200 ÃÂ¢ÃÂÃÂ¬</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1533,12 +1534,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RSA non majorÃ©</t>
+          <t>RSA non majorÃÂÃÂ©</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Entre 600 et 799 â¬</t>
+          <t>Entre 600 et 799 ÃÂ¢ÃÂÃÂ¬</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1548,12 +1549,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RSA non majorÃ©</t>
+          <t>RSA non majorÃÂÃÂ©</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Entre 400 et 599 â¬</t>
+          <t>Entre 400 et 599 ÃÂ¢ÃÂÃÂ¬</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2726,7 +2727,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ÃÂ 80 %</t>
+          <t>ÃÂÃÂÃÂÃÂ 80 %</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3604,261 +3605,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>bloc</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>cle</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>valeur</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>unite</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>are_coef_partie_variable</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.404</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>taux</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ARE : part du SJR (40,4 %)</t>
-        </is>
+          <t>repartition2025</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>microEntrepreneurs</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>758600</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>are_partie_fixe</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>13.19</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>euros/jour</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ARE : partie fixe par jour (2026)</t>
-        </is>
+          <t>repartition2025</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>societes</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>301300</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>are_coef_min</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>taux</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ARE : 57 % du SJR (minimum garanti)</t>
-        </is>
+          <t>repartition2025</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>entreprisesIndividuellesClassiques</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>105900</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>are_plancher_jour</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>31.97</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>euros/jour</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ARE : allocation journalière minimale (2026)</t>
-        </is>
+          <t>partMicro</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>are_plafond_coef</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>taux</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ARE : allocation &lt;= 75 % du salaire journalier de référence</t>
-        </is>
+          <t>partMicro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>are_jours_min</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>130</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>jours</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ARE : jours travaillés exigés sur les 24 derniers mois</t>
-        </is>
+          <t>perennite5ans</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>societes</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cotis_chomage_salarie_pct</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Cotisation chômage des salariés : 0 % depuis 2018</t>
-        </is>
+          <t>perennite5ans</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>entreprisesIndividuellesClassiques</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cotis_chomage_employeur_pct</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Cotisation chômage payée uniquement par l'employeur</t>
-        </is>
+          <t>perennite5ans</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>microAyantDemarre</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rsa_socle</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>651.6900000000001</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>euros/mois</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>RSA socle pour une personne seule (2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>smic_horaire_brut</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>euros/h</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SMIC horaire brut (2026) — à ajuster chaque année</t>
-        </is>
+          <t>perennite5ans</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>microToutesImmatriculations</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ppa_exonerations_patronales_md</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>80</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Md€/an</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Exonérations de cotisations patronales (voir page économie)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t># Feuille : constantes</t>
+          <t># Feuille : creations_entreprises</t>
         </is>
       </c>
     </row>
@@ -8697,6 +8607,275 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cle</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>valeur</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>unite</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>are_coef_partie_variable</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>taux</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ARE : part du SJR (40,4 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>are_partie_fixe</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>euros/jour</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ARE : partie fixe par jour (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>are_coef_min</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>taux</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ARE : 57 % du SJR (minimum garanti)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>are_plancher_jour</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>euros/jour</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ARE : allocation journalière minimale (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>are_plafond_coef</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>taux</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ARE : allocation &lt;= 75 % du salaire journalier de référence</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>are_jours_min</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>130</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>jours</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ARE : jours travaillés exigés sur les 24 derniers mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cotis_chomage_salarie_pct</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Cotisation chômage des salariés : 0 % depuis 2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cotis_chomage_employeur_pct</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Cotisation chômage payée uniquement par l'employeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>rsa_socle</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>651.6900000000001</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>euros/mois</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RSA socle pour une personne seule (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>smic_horaire_brut</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>euros/h</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SMIC horaire brut (2026) — à ajuster chaque année</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ppa_exonerations_patronales_md</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>80</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Md€/an</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Exonérations de cotisations patronales (voir page économie)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t># Feuille : constantes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -52797,7 +52976,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25 Ã  49 ans</t>
+          <t>25 ÃÂÃÂ  49 ans</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -52872,7 +53051,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25 Ã  49 ans</t>
+          <t>25 ÃÂÃÂ  49 ans</t>
         </is>
       </c>
       <c r="E7" t="n">

--- a/data/emploi/emploi.xlsx
+++ b/data/emploi/emploi.xlsx
@@ -26,7 +26,8 @@
     <sheet name="temps_partiel_quotite" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="emplois_vacants" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="creations_entreprises" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="constantes" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="desindustrialisation" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="constantes" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1429,12 +1430,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RSA majorÃÂÃÂ©</t>
+          <t>RSA majore</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Entre 400 et 599 ÃÂ¢ÃÂÃÂ¬</t>
+          <t>Entre 400 et 599 EUR</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1444,12 +1445,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RSA non majorÃÂÃÂ©</t>
+          <t>RSA non majore</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Entre 200 et 399 ÃÂ¢ÃÂÃÂ¬</t>
+          <t>Entre 200 et 399 EUR</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1459,12 +1460,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RSA non majorÃÂÃÂ©</t>
+          <t>RSA non majore</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>800 ÃÂ¢ÃÂÃÂ¬ ou plus</t>
+          <t>800 EUR ou plus</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1474,12 +1475,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RSA majorÃÂÃÂ©</t>
+          <t>RSA majore</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Entre 600 et 799 ÃÂ¢ÃÂÃÂ¬</t>
+          <t>Entre 600 et 799 EUR</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1489,12 +1490,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RSA majorÃÂÃÂ©</t>
+          <t>RSA majore</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Entre 200 et 399 ÃÂ¢ÃÂÃÂ¬</t>
+          <t>Entre 200 et 399 EUR</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1504,12 +1505,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RSA majorÃÂÃÂ©</t>
+          <t>RSA majore</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>800 ÃÂ¢ÃÂÃÂ¬ ou plus</t>
+          <t>800 EUR ou plus</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1519,12 +1520,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RSA non majorÃÂÃÂ©</t>
+          <t>RSA non majore</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Moins de 200 ÃÂ¢ÃÂÃÂ¬</t>
+          <t>Moins de 200 EUR</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1534,12 +1535,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RSA non majorÃÂÃÂ©</t>
+          <t>RSA non majore</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Entre 600 et 799 ÃÂ¢ÃÂÃÂ¬</t>
+          <t>Entre 600 et 799 EUR</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1549,12 +1550,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RSA non majorÃÂÃÂ©</t>
+          <t>RSA non majore</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Entre 400 et 599 ÃÂ¢ÃÂÃÂ¬</t>
+          <t>Entre 400 et 599 EUR</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2727,7 +2728,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ÃÂÃÂÃÂÃÂ 80 %</t>
+          <t>A 80 %</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -8613,6 +8614,257 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>bloc</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>annee</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>valeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>emploi_industrie</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>emploi_industrie</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1989</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4551</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>emploi_industrie</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4043</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>emploi_industrie</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3180</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>emploi_industrie</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>part_pib</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1980</v>
+      </c>
+      <c r="C7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>part_pib</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>creations_total</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C9" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>creations_societes</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C10" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>creations_total</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>creations_societes</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C12" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>creations_total</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1051.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>creations_total</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1111.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>creations_total</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1165.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>creations_societes</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" t="n">
+        <v>301.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>creations_micro</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="n">
+        <v>758.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t># Feuille : desindustrialisation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -52976,7 +53228,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25 ÃÂÃÂ  49 ans</t>
+          <t>25 a 49 ans</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -53051,7 +53303,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25 ÃÂÃÂ  49 ans</t>
+          <t>25 a 49 ans</t>
         </is>
       </c>
       <c r="E7" t="n">

--- a/data/emploi/emploi.xlsx
+++ b/data/emploi/emploi.xlsx
@@ -8614,7 +8614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8798,14 +8798,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>creations_total</t>
+          <t>creations_societes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C14" t="n">
-        <v>1111.2</v>
+        <v>269.9</v>
       </c>
     </row>
     <row r="15">
@@ -8815,10 +8815,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C15" t="n">
-        <v>1165.8</v>
+        <v>1111.2</v>
       </c>
     </row>
     <row r="16">
@@ -8828,27 +8828,53 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C16" t="n">
-        <v>301.3</v>
+        <v>284.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>creations_micro</t>
+          <t>creations_total</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2025</v>
       </c>
       <c r="C17" t="n">
-        <v>758.6</v>
+        <v>1165.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>creations_societes</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C18" t="n">
+        <v>301.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
+        <is>
+          <t>creations_micro</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C19" t="n">
+        <v>758.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t># Feuille : desindustrialisation</t>
         </is>

--- a/data/emploi/emploi.xlsx
+++ b/data/emploi/emploi.xlsx
@@ -8614,7 +8614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8707,174 +8707,213 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>part_pib</t>
+          <t>emploi_industrie</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1980</v>
+        <v>2023</v>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>part_pib</t>
+          <t>emploi_industrie</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="C8" t="n">
-        <v>12.6</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>creations_total</t>
+          <t>part_pib</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2000</v>
+        <v>1980</v>
       </c>
       <c r="C9" t="n">
-        <v>238</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>creations_societes</t>
+          <t>part_pib</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2000</v>
+        <v>2016</v>
       </c>
       <c r="C10" t="n">
-        <v>90</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>creations_total</t>
+          <t>part_pib</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C11" t="n">
-        <v>1066</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>creations_societes</t>
+          <t>creations_total</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2022</v>
+        <v>2000</v>
       </c>
       <c r="C12" t="n">
-        <v>290</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>creations_total</t>
+          <t>creations_societes</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2023</v>
+        <v>2000</v>
       </c>
       <c r="C13" t="n">
-        <v>1051.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>creations_societes</t>
+          <t>creations_total</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C14" t="n">
-        <v>269.9</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>creations_total</t>
+          <t>creations_societes</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C15" t="n">
-        <v>1111.2</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>creations_societes</t>
+          <t>creations_total</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C16" t="n">
-        <v>284.6</v>
+        <v>1051.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>creations_total</t>
+          <t>creations_societes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C17" t="n">
-        <v>1165.8</v>
+        <v>269.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>creations_societes</t>
+          <t>creations_total</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C18" t="n">
-        <v>301.3</v>
+        <v>1111.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>creations_micro</t>
+          <t>creations_societes</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C19" t="n">
+        <v>284.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>creations_total</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>2025</v>
       </c>
-      <c r="C19" t="n">
-        <v>758.6</v>
+      <c r="C20" t="n">
+        <v>1165.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
+        <is>
+          <t>creations_societes</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C21" t="n">
+        <v>301.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>creations_micro</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C22" t="n">
+        <v>758.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t># Feuille : desindustrialisation</t>
         </is>

--- a/data/emploi/emploi.xlsx
+++ b/data/emploi/emploi.xlsx
@@ -27,7 +27,8 @@
     <sheet name="emplois_vacants" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="creations_entreprises" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="desindustrialisation" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="constantes" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="hl_secteurs" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="constantes" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8930,6 +8931,396 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>bloc</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>cle</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>valeur</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>anneeRef</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>emploisTotal</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>80200</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insee Analyses ARA n. 67 (2017, donnees 2015) - insee.fr/fr/statistiques/3635722</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>spheres</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>productive1975</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>spheres</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>productive2015</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>spheres</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>presentielle1975</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>spheres</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>presentielle2015</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>parts</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>industrie</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>parts</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>industrieFrance</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>parts</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>santeActionSociale</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>parts</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>santeActionSocialeAra</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>parts</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>adminPubliqueVelay</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>parts</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>agriculteurs</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>parts</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>agriculteursFrance</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>parts</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>cadres</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>parts</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>cadresAra</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>parts</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>tempsPartielFemmes</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>parts</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>tempsPartielFemmesAra</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>parts</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>interimBrioude</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>industrie</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>caoutchoucPlastique</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>industrie</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>textile</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>industrie</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>partCaoutchoucPlastique</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>industrie</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>baisseIndustrieBrioude2005_2015</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t># Feuille : hl_secteurs</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
